--- a/artfynd/A 55261-2025 artfynd.xlsx
+++ b/artfynd/A 55261-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688149</v>
       </c>
       <c r="B2" t="n">
-        <v>92902</v>
+        <v>92907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55261-2025 artfynd.xlsx
+++ b/artfynd/A 55261-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688149</v>
       </c>
       <c r="B2" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55261-2025 artfynd.xlsx
+++ b/artfynd/A 55261-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688149</v>
       </c>
       <c r="B2" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55261-2025 artfynd.xlsx
+++ b/artfynd/A 55261-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688149</v>
       </c>
       <c r="B2" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55261-2025 artfynd.xlsx
+++ b/artfynd/A 55261-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688149</v>
       </c>
       <c r="B2" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55261-2025 artfynd.xlsx
+++ b/artfynd/A 55261-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688149</v>
       </c>
       <c r="B2" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55261-2025 artfynd.xlsx
+++ b/artfynd/A 55261-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688149</v>
       </c>
       <c r="B2" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55261-2025 artfynd.xlsx
+++ b/artfynd/A 55261-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688149</v>
       </c>
       <c r="B2" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55261-2025 artfynd.xlsx
+++ b/artfynd/A 55261-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688149</v>
       </c>
       <c r="B2" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
